--- a/results/components/gene_names/p7s5.xlsx
+++ b/results/components/gene_names/p7s5.xlsx
@@ -22,10 +22,10 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
+    <t>Ef1gamma</t>
   </si>
   <si>
-    <t>Ark</t>
+    <t>tin</t>
   </si>
 </sst>
 </file>

--- a/results/components/gene_names/p7s5.xlsx
+++ b/results/components/gene_names/p7s5.xlsx
@@ -22,10 +22,10 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
+    <t>Syx1A</t>
   </si>
   <si>
-    <t>tin</t>
+    <t>CG32082</t>
   </si>
 </sst>
 </file>
